--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -721,7 +721,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: kwaz1243, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7626,14 +7626,14 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7714,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7734,14 +7734,14 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10333,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10407,14 +10407,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10461,14 +10461,14 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10515,14 +10515,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10677,14 +10677,14 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10704,14 +10704,14 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10731,14 +10731,14 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10785,14 +10785,14 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10812,14 +10812,14 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10839,14 +10839,14 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13944,7 +13944,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15051,14 +15051,14 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -15159,14 +15159,14 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15213,14 +15213,14 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -15240,14 +15240,14 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -15267,14 +15267,14 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15402,14 +15402,14 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -15510,14 +15510,14 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15564,14 +15564,14 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -15591,14 +15591,14 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -15618,14 +15618,14 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19290,7 +19290,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19614,7 +19614,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20235,14 +20235,14 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20350,7 +20350,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20397,14 +20397,14 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22233,7 +22233,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22746,7 +22746,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22861,7 +22861,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -22881,14 +22881,14 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -22908,14 +22908,14 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -22969,7 +22969,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -22989,14 +22989,14 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -23016,14 +23016,14 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23637,7 +23637,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23745,7 +23745,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23772,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23799,7 +23799,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24150,7 +24150,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24258,7 +24258,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24312,7 +24312,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24555,14 +24555,14 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -24582,14 +24582,14 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -24609,14 +24609,14 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -24636,14 +24636,14 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24717,14 +24717,14 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -24744,14 +24744,14 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -24771,14 +24771,14 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -24798,14 +24798,14 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24879,14 +24879,14 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -24906,14 +24906,14 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -24933,14 +24933,14 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -24960,14 +24960,14 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25554,7 +25554,7 @@
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27552,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28173,7 +28173,7 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28470,7 +28470,7 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28578,7 +28578,7 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28605,7 +28605,7 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29334,7 +29334,7 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29388,7 +29388,7 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29442,7 +29442,7 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29469,7 +29469,7 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29496,7 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29793,7 +29793,7 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31494,7 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31548,7 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31798,7 +31798,7 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -31879,7 +31879,7 @@
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
@@ -31899,14 +31899,14 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
@@ -31926,7 +31926,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -31960,7 +31960,7 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -32041,7 +32041,7 @@
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
@@ -32061,14 +32061,14 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32304,7 +32304,7 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32601,7 +32601,7 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32628,7 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32763,7 +32763,7 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32790,7 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32844,7 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32871,7 +32871,7 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33033,7 +33033,7 @@
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33060,7 +33060,7 @@
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33087,7 +33087,7 @@
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33114,7 +33114,7 @@
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33141,7 +33141,7 @@
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33168,7 +33168,7 @@
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33195,7 +33195,7 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33222,7 @@
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33303,7 +33303,7 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33384,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33519,7 +33519,7 @@
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33762,7 +33762,7 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33789,7 +33789,7 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33870,7 +33870,7 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34167,7 +34167,7 @@
       </c>
       <c r="E1250" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="E1252" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34248,7 +34248,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35220,7 +35220,7 @@
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35247,7 +35247,7 @@
       </c>
       <c r="E1290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35274,7 @@
       </c>
       <c r="E1291" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="E1304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35652,7 +35652,7 @@
       </c>
       <c r="E1305" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35733,7 +35733,7 @@
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36354,7 +36354,7 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36489,7 +36489,7 @@
       </c>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="E1339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36597,7 +36597,7 @@
       </c>
       <c r="E1340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36705,7 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36732,7 +36732,7 @@
       </c>
       <c r="E1345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36840,7 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36867,7 +36867,7 @@
       </c>
       <c r="E1350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36894,7 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="E1354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="E1355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37056,7 +37056,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37083,7 +37083,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="E1361" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37299,7 +37299,7 @@
       </c>
       <c r="E1366" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37461,7 +37461,7 @@
       </c>
       <c r="E1372" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37515,7 +37515,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37596,7 +37596,7 @@
       </c>
       <c r="E1377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37650,7 +37650,7 @@
       </c>
       <c r="E1379" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37677,7 +37677,7 @@
       </c>
       <c r="E1380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="E1382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="E1383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37866,7 +37866,7 @@
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37893,7 +37893,7 @@
       </c>
       <c r="E1388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="E1395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38217,7 +38217,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38271,7 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38352,7 +38352,7 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38433,7 +38433,7 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38487,7 +38487,7 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39189,7 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39216,7 +39216,7 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39270,7 +39270,7 @@
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39297,7 +39297,7 @@
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39324,7 @@
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39351,7 +39351,7 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39378,7 +39378,7 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39405,7 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39459,7 +39459,7 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39486,7 +39486,7 @@
       </c>
       <c r="E1447" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39513,7 +39513,7 @@
       </c>
       <c r="E1448" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39567,7 +39567,7 @@
       </c>
       <c r="E1450" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39594,7 +39594,7 @@
       </c>
       <c r="E1451" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39675,7 +39675,7 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39702,7 +39702,7 @@
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39729,7 +39729,7 @@
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39783,7 +39783,7 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39810,7 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39837,7 +39837,7 @@
       </c>
       <c r="E1460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39864,7 +39864,7 @@
       </c>
       <c r="E1461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39891,7 +39891,7 @@
       </c>
       <c r="E1462" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39918,7 +39918,7 @@
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39945,7 +39945,7 @@
       </c>
       <c r="E1464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39972,7 +39972,7 @@
       </c>
       <c r="E1465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39999,7 +39999,7 @@
       </c>
       <c r="E1466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40026,7 +40026,7 @@
       </c>
       <c r="E1467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40053,7 +40053,7 @@
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40107,7 +40107,7 @@
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40134,7 +40134,7 @@
       </c>
       <c r="E1471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40161,7 +40161,7 @@
       </c>
       <c r="E1472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40188,7 +40188,7 @@
       </c>
       <c r="E1473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40215,7 +40215,7 @@
       </c>
       <c r="E1474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40242,7 +40242,7 @@
       </c>
       <c r="E1475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40323,7 +40323,7 @@
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40377,7 +40377,7 @@
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40404,7 +40404,7 @@
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41079,7 +41079,7 @@
       </c>
       <c r="E1506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41106,7 +41106,7 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41133,7 +41133,7 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41160,7 +41160,7 @@
       </c>
       <c r="E1509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41187,7 +41187,7 @@
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41241,7 +41241,7 @@
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="E1513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41295,7 +41295,7 @@
       </c>
       <c r="E1514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41322,7 +41322,7 @@
       </c>
       <c r="E1515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41349,7 +41349,7 @@
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41376,7 +41376,7 @@
       </c>
       <c r="E1517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41862,7 +41862,7 @@
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41889,7 +41889,7 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41943,7 +41943,7 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41970,7 +41970,7 @@
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41997,7 +41997,7 @@
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42051,7 +42051,7 @@
       </c>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42078,7 +42078,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42105,7 +42105,7 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42132,7 +42132,7 @@
       </c>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42213,7 +42213,7 @@
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42240,7 +42240,7 @@
       </c>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42267,7 +42267,7 @@
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42294,7 +42294,7 @@
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42348,7 +42348,7 @@
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42375,7 +42375,7 @@
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42429,7 +42429,7 @@
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43165,7 +43165,7 @@
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1584" t="inlineStr">
@@ -43185,14 +43185,14 @@
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1585" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43246,7 +43246,7 @@
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
@@ -43266,14 +43266,14 @@
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1588" t="inlineStr">
@@ -43293,14 +43293,14 @@
       </c>
       <c r="E1588" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
@@ -43320,14 +43320,14 @@
       </c>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1590" t="inlineStr">
@@ -43347,14 +43347,14 @@
       </c>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
@@ -43374,14 +43374,14 @@
       </c>
       <c r="E1591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1592" t="inlineStr">
@@ -43401,7 +43401,7 @@
       </c>
       <c r="E1592" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43948,7 +43948,7 @@
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
@@ -43968,14 +43968,14 @@
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1614" t="inlineStr">
@@ -43995,14 +43995,14 @@
       </c>
       <c r="E1614" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
@@ -44022,14 +44022,14 @@
       </c>
       <c r="E1615" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
@@ -44049,14 +44049,14 @@
       </c>
       <c r="E1616" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -44076,14 +44076,14 @@
       </c>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1618" t="inlineStr">
@@ -44103,14 +44103,14 @@
       </c>
       <c r="E1618" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1619" t="inlineStr">
@@ -44130,14 +44130,14 @@
       </c>
       <c r="E1619" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1620" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="E1620" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -44832,7 +44832,7 @@
       </c>
       <c r="E1645" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44859,7 +44859,7 @@
       </c>
       <c r="E1646" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44940,7 +44940,7 @@
       </c>
       <c r="E1649" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44967,7 +44967,7 @@
       </c>
       <c r="E1650" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -45264,7 +45264,7 @@
       </c>
       <c r="E1661" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45291,7 +45291,7 @@
       </c>
       <c r="E1662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45318,7 +45318,7 @@
       </c>
       <c r="E1663" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45345,7 +45345,7 @@
       </c>
       <c r="E1664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45426,7 +45426,7 @@
       </c>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="E1668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="E1669" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45507,7 +45507,7 @@
       </c>
       <c r="E1670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="E1677" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45723,7 +45723,7 @@
       </c>
       <c r="E1678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45750,7 +45750,7 @@
       </c>
       <c r="E1679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45777,7 +45777,7 @@
       </c>
       <c r="E1680" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="E1682" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45858,7 +45858,7 @@
       </c>
       <c r="E1683" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45885,7 +45885,7 @@
       </c>
       <c r="E1684" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45939,7 +45939,7 @@
       </c>
       <c r="E1686" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45966,7 +45966,7 @@
       </c>
       <c r="E1687" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46020,7 +46020,7 @@
       </c>
       <c r="E1689" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46047,7 +46047,7 @@
       </c>
       <c r="E1690" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46074,7 +46074,7 @@
       </c>
       <c r="E1691" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46101,7 +46101,7 @@
       </c>
       <c r="E1692" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46155,7 +46155,7 @@
       </c>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46182,7 +46182,7 @@
       </c>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46209,7 +46209,7 @@
       </c>
       <c r="E1696" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46263,7 +46263,7 @@
       </c>
       <c r="E1698" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46290,7 +46290,7 @@
       </c>
       <c r="E1699" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46506,7 +46506,7 @@
       </c>
       <c r="E1707" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46533,7 +46533,7 @@
       </c>
       <c r="E1708" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46560,7 +46560,7 @@
       </c>
       <c r="E1709" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46587,7 +46587,7 @@
       </c>
       <c r="E1710" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46803,7 +46803,7 @@
       </c>
       <c r="E1718" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46830,7 +46830,7 @@
       </c>
       <c r="E1719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46884,7 +46884,7 @@
       </c>
       <c r="E1721" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46911,7 +46911,7 @@
       </c>
       <c r="E1722" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46938,7 +46938,7 @@
       </c>
       <c r="E1723" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46992,7 +46992,7 @@
       </c>
       <c r="E1725" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -47019,7 +47019,7 @@
       </c>
       <c r="E1726" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -47073,7 +47073,7 @@
       </c>
       <c r="E1728" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -47100,7 +47100,7 @@
       </c>
       <c r="E1729" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -47127,7 +47127,7 @@
       </c>
       <c r="E1730" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1902,14 +1902,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1983,14 +1983,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: kuna1268, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7572,14 +7572,14 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7626,14 +7626,14 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7653,14 +7653,14 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7680,14 +7680,14 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7707,14 +7707,14 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7734,14 +7734,14 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7842,14 +7842,14 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7869,14 +7869,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10299,14 +10299,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10326,14 +10326,14 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10407,14 +10407,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10434,14 +10434,14 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10461,14 +10461,14 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10515,14 +10515,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10542,14 +10542,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10596,14 +10596,14 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10623,14 +10623,14 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10650,14 +10650,14 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10677,14 +10677,14 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10704,14 +10704,14 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10731,14 +10731,14 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10758,14 +10758,14 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10785,14 +10785,14 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10812,14 +10812,14 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10839,14 +10839,14 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10866,14 +10866,14 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10893,14 +10893,14 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15024,14 +15024,14 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -15051,14 +15051,14 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -15078,14 +15078,14 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15186,14 +15186,14 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15240,14 +15240,14 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -15267,14 +15267,14 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -15294,14 +15294,14 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15348,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15375,14 +15375,14 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -15402,14 +15402,14 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -15429,14 +15429,14 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15537,14 +15537,14 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15591,14 +15591,14 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -15618,14 +15618,14 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18156,7 +18156,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18210,7 +18210,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19155,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19182,7 +19182,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19290,7 +19290,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19506,7 +19506,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19614,7 +19614,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20161,7 +20161,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -20181,14 +20181,14 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -20208,14 +20208,14 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -20289,14 +20289,14 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -20316,14 +20316,14 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -20343,14 +20343,14 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -20370,14 +20370,14 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -20451,14 +20451,14 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20586,7 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20694,7 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22233,7 +22233,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -22854,14 +22854,14 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -22881,14 +22881,14 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -22908,14 +22908,14 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -22935,14 +22935,14 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -22962,14 +22962,14 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -22989,14 +22989,14 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -23016,14 +23016,14 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -23043,7 +23043,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23637,7 +23637,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23745,7 +23745,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23772,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23799,7 +23799,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24238,7 +24238,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -24258,14 +24258,14 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24339,14 +24339,14 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -24366,14 +24366,14 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -24393,14 +24393,14 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -24420,14 +24420,14 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,14 +24501,14 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -24528,14 +24528,14 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -24555,14 +24555,14 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24663,14 +24663,14 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -24690,14 +24690,14 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24960,7 +24960,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25230,7 +25230,7 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25338,7 +25338,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25392,7 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25770,7 +25770,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25986,7 +25986,7 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26418,7 +26418,7 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27498,7 +27498,7 @@
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27552,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27606,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29314,7 +29314,7 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29388,7 +29388,7 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29469,14 +29469,14 @@
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -29523,14 +29523,14 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
@@ -29550,7 +29550,7 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29604,7 +29604,7 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29685,7 +29685,7 @@
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29712,14 +29712,14 @@
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
@@ -29739,7 +29739,7 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -29793,14 +29793,14 @@
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
@@ -29820,14 +29820,14 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
@@ -29847,14 +29847,14 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -29908,7 +29908,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
@@ -29928,14 +29928,14 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
@@ -29955,14 +29955,14 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
@@ -29982,14 +29982,14 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
@@ -30009,14 +30009,14 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
@@ -30036,7 +30036,7 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -30070,7 +30070,7 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
@@ -30090,14 +30090,14 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
@@ -30117,7 +30117,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role P in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: tusc1257, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30252,7 @@
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30333,7 +30333,7 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30441,7 +30441,7 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30576,7 +30576,7 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30792,7 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30873,7 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31062,7 +31062,7 @@
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31089,7 +31089,7 @@
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31170,7 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31494,7 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31548,7 +31548,7 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31818,7 +31818,7 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31845,7 +31845,7 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -31953,7 +31953,7 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32061,7 +32061,7 @@
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32088,7 @@
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32304,7 +32304,7 @@
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33195,7 +33195,7 @@
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33222,7 @@
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33303,7 +33303,7 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33330,7 +33330,7 @@
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33357,7 +33357,7 @@
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33384,7 +33384,7 @@
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33438,7 +33438,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33465,7 +33465,7 @@
       </c>
       <c r="E1224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33568,12 +33568,12 @@
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>AWM, NCP</t>
+          <t>AWM</t>
         </is>
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-non.human and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33595,12 +33595,12 @@
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>AWM, NCP</t>
+          <t>AWM</t>
         </is>
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-non.human and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33622,12 +33622,12 @@
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>AWM</t>
+          <t>AWM, NCP</t>
         </is>
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-non.human and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33649,12 +33649,12 @@
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>AWM</t>
+          <t>AWM, NCP</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-non.human and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33735,7 +33735,7 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33789,7 +33789,7 @@
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33816,7 +33816,7 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33870,7 +33870,7 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33951,7 +33951,7 @@
       </c>
       <c r="E1242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33978,7 +33978,7 @@
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34032,7 +34032,7 @@
       </c>
       <c r="E1245" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34059,7 +34059,7 @@
       </c>
       <c r="E1246" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="E1248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34626,7 @@
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34761,7 +34761,7 @@
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34788,7 +34788,7 @@
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34842,7 +34842,7 @@
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34923,7 +34923,7 @@
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34977,7 +34977,7 @@
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35004,7 +35004,7 @@
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35058,7 +35058,7 @@
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35085,7 +35085,7 @@
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35112,7 @@
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35139,7 +35139,7 @@
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="E1288" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35220,7 +35220,7 @@
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35247,7 +35247,7 @@
       </c>
       <c r="E1290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35274,7 @@
       </c>
       <c r="E1291" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35301,7 +35301,7 @@
       </c>
       <c r="E1292" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35328,7 +35328,7 @@
       </c>
       <c r="E1293" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="E1298" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="E1299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35598,7 @@
       </c>
       <c r="E1303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35787,7 +35787,7 @@
       </c>
       <c r="E1310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
       </c>
       <c r="E1311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36138,7 +36138,7 @@
       </c>
       <c r="E1323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36219,7 +36219,7 @@
       </c>
       <c r="E1326" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36327,7 +36327,7 @@
       </c>
       <c r="E1330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36354,7 +36354,7 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="E1339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36597,7 +36597,7 @@
       </c>
       <c r="E1340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="E1341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36705,7 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36840,7 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36867,7 +36867,7 @@
       </c>
       <c r="E1350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36894,7 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="E1354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37056,7 +37056,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37083,7 +37083,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="E1361" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37245,7 +37245,7 @@
       </c>
       <c r="E1364" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37272,7 +37272,7 @@
       </c>
       <c r="E1365" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37326,7 +37326,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37515,7 +37515,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37596,7 +37596,7 @@
       </c>
       <c r="E1377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="E1406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
       </c>
       <c r="E1407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38433,7 +38433,7 @@
       </c>
       <c r="E1408" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="E1409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38487,7 +38487,7 @@
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
       </c>
       <c r="E1411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38595,7 +38595,7 @@
       </c>
       <c r="E1414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38622,7 +38622,7 @@
       </c>
       <c r="E1415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38649,7 +38649,7 @@
       </c>
       <c r="E1416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38676,7 +38676,7 @@
       </c>
       <c r="E1417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38703,7 +38703,7 @@
       </c>
       <c r="E1418" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38757,7 +38757,7 @@
       </c>
       <c r="E1420" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38784,7 +38784,7 @@
       </c>
       <c r="E1421" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38811,7 +38811,7 @@
       </c>
       <c r="E1422" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38838,7 +38838,7 @@
       </c>
       <c r="E1423" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38865,7 +38865,7 @@
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38892,7 +38892,7 @@
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38973,7 +38973,7 @@
       </c>
       <c r="E1428" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39000,7 +39000,7 @@
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39027,7 +39027,7 @@
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39054,7 +39054,7 @@
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39189,7 @@
       </c>
       <c r="E1436" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39216,7 +39216,7 @@
       </c>
       <c r="E1437" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39270,7 +39270,7 @@
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39351,7 +39351,7 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39378,7 +39378,7 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39405,7 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39459,7 +39459,7 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40323,7 +40323,7 @@
       </c>
       <c r="E1478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40377,7 +40377,7 @@
       </c>
       <c r="E1480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40404,7 +40404,7 @@
       </c>
       <c r="E1481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40485,7 +40485,7 @@
       </c>
       <c r="E1484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40512,7 +40512,7 @@
       </c>
       <c r="E1485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40539,7 +40539,7 @@
       </c>
       <c r="E1486" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40566,7 +40566,7 @@
       </c>
       <c r="E1487" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41106,7 +41106,7 @@
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41133,7 +41133,7 @@
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41241,7 +41241,7 @@
       </c>
       <c r="E1512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41322,7 +41322,7 @@
       </c>
       <c r="E1515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41349,7 +41349,7 @@
       </c>
       <c r="E1516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41430,7 +41430,7 @@
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41457,7 +41457,7 @@
       </c>
       <c r="E1520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41538,7 +41538,7 @@
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41565,7 +41565,7 @@
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41619,7 +41619,7 @@
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42127,7 +42127,7 @@
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>AN, AWM</t>
+          <t>DI, NCP</t>
         </is>
       </c>
       <c r="E1545" t="inlineStr">
@@ -42154,7 +42154,7 @@
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>DI, NCP</t>
+          <t>AN, AWM</t>
         </is>
       </c>
       <c r="E1546" t="inlineStr">
@@ -42181,7 +42181,7 @@
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>AN, AWM</t>
+          <t>DI, NCP</t>
         </is>
       </c>
       <c r="E1547" t="inlineStr">
@@ -42208,7 +42208,7 @@
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>DI, NCP</t>
+          <t>AN, AWM</t>
         </is>
       </c>
       <c r="E1548" t="inlineStr">
@@ -42463,7 +42463,7 @@
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
@@ -42483,14 +42483,14 @@
       </c>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
@@ -42510,7 +42510,7 @@
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42672,7 +42672,7 @@
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42699,7 +42699,7 @@
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43192,7 +43192,7 @@
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1585" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43239,14 +43239,14 @@
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
@@ -43266,7 +43266,7 @@
       </c>
       <c r="E1587" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43300,7 +43300,7 @@
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
@@ -43320,7 +43320,7 @@
       </c>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43347,14 +43347,14 @@
       </c>
       <c r="E1590" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
@@ -43374,7 +43374,7 @@
       </c>
       <c r="E1591" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -44076,7 +44076,7 @@
       </c>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44103,7 +44103,7 @@
       </c>
       <c r="E1618" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44130,7 +44130,7 @@
       </c>
       <c r="E1619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44157,7 +44157,7 @@
       </c>
       <c r="E1620" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44184,7 +44184,7 @@
       </c>
       <c r="E1621" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44211,7 +44211,7 @@
       </c>
       <c r="E1622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44454,7 +44454,7 @@
       </c>
       <c r="E1631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44481,7 +44481,7 @@
       </c>
       <c r="E1632" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44508,7 +44508,7 @@
       </c>
       <c r="E1633" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44535,7 +44535,7 @@
       </c>
       <c r="E1634" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44562,7 +44562,7 @@
       </c>
       <c r="E1635" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44589,7 +44589,7 @@
       </c>
       <c r="E1636" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44616,7 +44616,7 @@
       </c>
       <c r="E1637" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44643,7 +44643,7 @@
       </c>
       <c r="E1638" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
       </c>
       <c r="E1639" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44697,7 +44697,7 @@
       </c>
       <c r="E1640" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44724,7 +44724,7 @@
       </c>
       <c r="E1641" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44751,7 +44751,7 @@
       </c>
       <c r="E1642" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44940,7 +44940,7 @@
       </c>
       <c r="E1649" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -44967,7 +44967,7 @@
       </c>
       <c r="E1650" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45021,7 +45021,7 @@
       </c>
       <c r="E1652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45048,7 +45048,7 @@
       </c>
       <c r="E1653" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="E1654" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45102,7 +45102,7 @@
       </c>
       <c r="E1655" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45129,7 +45129,7 @@
       </c>
       <c r="E1656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45156,7 +45156,7 @@
       </c>
       <c r="E1657" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45183,7 +45183,7 @@
       </c>
       <c r="E1658" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45237,7 +45237,7 @@
       </c>
       <c r="E1660" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45264,7 +45264,7 @@
       </c>
       <c r="E1661" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45291,7 +45291,7 @@
       </c>
       <c r="E1662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45345,7 +45345,7 @@
       </c>
       <c r="E1664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45372,7 +45372,7 @@
       </c>
       <c r="E1665" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45399,7 +45399,7 @@
       </c>
       <c r="E1666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45426,7 +45426,7 @@
       </c>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="E1668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="E1669" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45507,7 +45507,7 @@
       </c>
       <c r="E1670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45561,7 +45561,7 @@
       </c>
       <c r="E1672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46020,7 +46020,7 @@
       </c>
       <c r="E1689" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46047,7 +46047,7 @@
       </c>
       <c r="E1690" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46074,7 +46074,7 @@
       </c>
       <c r="E1691" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46101,7 +46101,7 @@
       </c>
       <c r="E1692" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46155,7 +46155,7 @@
       </c>
       <c r="E1694" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46182,7 +46182,7 @@
       </c>
       <c r="E1695" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46209,7 +46209,7 @@
       </c>
       <c r="E1696" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46236,7 +46236,7 @@
       </c>
       <c r="E1697" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46263,7 +46263,7 @@
       </c>
       <c r="E1698" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46290,7 +46290,7 @@
       </c>
       <c r="E1699" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46344,7 +46344,7 @@
       </c>
       <c r="E1701" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46371,7 +46371,7 @@
       </c>
       <c r="E1702" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>

--- a/outputs/alignment-warnings.xlsx
+++ b/outputs/alignment-warnings.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7680,14 +7680,14 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -7869,14 +7869,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>3pl</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: wage1238, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 3pl and role P in language: wage1238, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: any and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10299,14 +10299,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10326,14 +10326,14 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10488,14 +10488,14 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10515,14 +10515,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10542,14 +10542,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10569,14 +10569,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10596,14 +10596,14 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10623,14 +10623,14 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10650,14 +10650,14 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10677,14 +10677,14 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10704,14 +10704,14 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.excl</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -10792,7 +10792,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10812,14 +10812,14 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10839,14 +10839,14 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1du.excl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10866,14 +10866,14 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.excl and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10893,14 +10893,14 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role P in language: coos1249, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.non-M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-indf and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high-def and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low-def and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low-indef and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14133,7 +14133,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15159,14 +15159,14 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -15267,14 +15267,14 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N1 and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15510,14 +15510,14 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N2 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -15537,7 +15537,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15598,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -15618,14 +15618,14 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: ngar1284, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -15996,7 +15996,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16158,7 +16158,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16401,7 +16401,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16779,7 +16779,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassD and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.ClassD and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassA and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassA and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.ClassC and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.ClassB and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.ClassB and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17508,7 +17508,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18102,7 +18102,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18345,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18615,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18831,7 +18831,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -18885,7 +18885,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19506,7 +19506,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du.incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19614,7 +19614,7 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2/3M and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2/3F and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20694,14 +20694,14 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -20721,7 +20721,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20748,14 +20748,14 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20809,7 +20809,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1sg</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20856,14 +20856,14 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>1sg</t>
+          <t>1pl</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1sg and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -20910,14 +20910,14 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role A in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>1pl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: yecu1235, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21234,7 +21234,7 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -21315,7 +21315,7 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21342,7 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21396,7 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21423,7 +21423,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21639,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21828,7 +21828,7 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E799" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="E801" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22098,7 +22098,7 @@
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22503,7 +22503,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22530,7 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22611,7 +22611,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22665,7 +22665,7 @@
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22746,7 +22746,7 @@
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22773,7 +22773,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22827,7 +22827,7 @@
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22935,7 +22935,7 @@
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22962,7 +22962,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -23232,7 +23232,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23313,14 +23313,14 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -23340,14 +23340,14 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -23367,14 +23367,14 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -23394,14 +23394,14 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -23421,14 +23421,14 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -23448,14 +23448,14 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -23475,14 +23475,14 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2du</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -23502,14 +23502,14 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2du</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -23529,7 +23529,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2du and role A in language: djam1255, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -23988,7 +23988,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24069,7 +24069,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24150,7 +24150,7 @@
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.M/F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M/F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24312,7 +24312,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24366,7 +24366,7 @@
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24447,7 +24447,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -24724,7 +24724,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -24744,14 +24744,14 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -24771,14 +24771,14 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -24798,14 +24798,14 @@
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -24879,14 +24879,14 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -24906,14 +24906,14 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -24933,14 +24933,14 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -24960,14 +24960,14 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25048,7 +25048,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -25068,14 +25068,14 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -25095,14 +25095,14 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>1du.incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -25122,7 +25122,7 @@
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25149,14 +25149,14 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1du.incl</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1du.incl and role A in language: wich1260, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25230,7 +25230,7 @@
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25257,7 +25257,7 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25338,7 +25338,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25392,7 @@
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25770,7 +25770,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25824,7 +25824,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nF and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26337,7 +26337,7 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26364,7 +26364,7 @@
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26418,7 +26418,7 @@
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.anim.fobv and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim.fobv and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.anim-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.anim-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26688,7 +26688,7 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26742,7 +26742,7 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26796,7 +26796,7 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26850,7 +26850,7 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26877,7 +26877,7 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26904,7 +26904,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27120,14 +27120,14 @@
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -27147,14 +27147,14 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -27208,7 +27208,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.incl</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -27228,14 +27228,14 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>1pl.incl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -27255,7 +27255,7 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.incl and role P in language: miri1266, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: miri1266, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27849,7 +27849,7 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +27876,7 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -27957,7 +27957,7 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28038,7 +28038,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28146,7 +28146,7 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28173,7 +28173,7 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28200,7 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28281,7 +28281,7 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28362,7 +28362,7 @@
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.N and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28470,7 +28470,7 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29928,7 +29928,7 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -29982,14 +29982,14 @@
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>1incl</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
@@ -30009,7 +30009,7 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -30036,14 +30036,14 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>1incl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1incl and role P in language: mund1330, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30117,7 +30117,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30225,7 @@
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30630,7 @@
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30765,7 +30765,7 @@
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30792,7 @@
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30873,7 +30873,7 @@
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31116,7 +31116,7 @@
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31170,7 @@
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31224,7 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31278,7 +31278,7 @@
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31332,7 @@
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31494,7 +31494,7 @@
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31602,7 +31602,7 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31629,7 +31629,7 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31656,7 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31710,7 +31710,7 @@
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31818,7 +31818,7 @@
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31845,7 +31845,7 @@
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31953,7 +31953,7 @@
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32358,7 +32358,7 @@
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32466,7 +32466,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32574,7 +32574,7 @@
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32601,7 +32601,7 @@
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32628,7 @@
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="E1197" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32763,7 +32763,7 @@
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32790,7 @@
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32817,7 +32817,7 @@
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32844,7 +32844,7 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32871,7 +32871,7 @@
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: S (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: S (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -32979,7 +32979,7 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33006,7 @@
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2du and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3du and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33708,7 +33708,7 @@
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33762,7 +33762,7 @@
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33816,7 +33816,7 @@
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33843,7 +33843,7 @@
       </c>
       <c r="E1238" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33870,7 +33870,7 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33924,7 +33924,7 @@
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -33978,7 +33978,7 @@
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -34248,7 +34248,7 @@
       </c>
       <c r="E1253" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34329,7 +34329,7 @@
       </c>
       <c r="E1256" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34356,7 +34356,7 @@
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34410,7 +34410,7 @@
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="E1260" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34491,7 +34491,7 @@
       </c>
       <c r="E1262" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34518,7 @@
       </c>
       <c r="E1263" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34572,7 +34572,7 @@
       </c>
       <c r="E1265" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34599,7 @@
       </c>
       <c r="E1266" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35112,7 +35112,7 @@
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35139,7 +35139,7 @@
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35247,7 +35247,7 @@
       </c>
       <c r="E1290" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35274,7 @@
       </c>
       <c r="E1291" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35301,7 +35301,7 @@
       </c>
       <c r="E1292" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35328,7 +35328,7 @@
       </c>
       <c r="E1293" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="E1294" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E1295" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35409,7 +35409,7 @@
       </c>
       <c r="E1296" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35436,7 @@
       </c>
       <c r="E1297" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="E1299" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35517,7 +35517,7 @@
       </c>
       <c r="E1300" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35544,7 +35544,7 @@
       </c>
       <c r="E1301" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="E1302" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35598,7 @@
       </c>
       <c r="E1303" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="E1304" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35679,7 +35679,7 @@
       </c>
       <c r="E1306" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="E1307" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35733,7 +35733,7 @@
       </c>
       <c r="E1308" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35760,7 +35760,7 @@
       </c>
       <c r="E1309" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35841,7 +35841,7 @@
       </c>
       <c r="E1312" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="E1313" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E1314" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35922,7 +35922,7 @@
       </c>
       <c r="E1315" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="E1316" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -35976,7 +35976,7 @@
       </c>
       <c r="E1317" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36003,7 +36003,7 @@
       </c>
       <c r="E1318" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="E1319" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36057,7 +36057,7 @@
       </c>
       <c r="E1320" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="E1321" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36111,7 @@
       </c>
       <c r="E1322" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36165,7 +36165,7 @@
       </c>
       <c r="E1324" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="E1325" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36246,7 +36246,7 @@
       </c>
       <c r="E1327" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="E1328" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E1329" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36327,7 +36327,7 @@
       </c>
       <c r="E1330" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36354,7 +36354,7 @@
       </c>
       <c r="E1331" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36381,7 +36381,7 @@
       </c>
       <c r="E1332" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E1333" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36435,7 @@
       </c>
       <c r="E1334" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E1335" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36489,7 +36489,7 @@
       </c>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36516,7 +36516,7 @@
       </c>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="E1338" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="E1339" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36597,7 +36597,7 @@
       </c>
       <c r="E1340" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="E1341" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36651,7 +36651,7 @@
       </c>
       <c r="E1342" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36678,7 +36678,7 @@
       </c>
       <c r="E1343" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36705,7 @@
       </c>
       <c r="E1344" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36732,7 +36732,7 @@
       </c>
       <c r="E1345" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="E1346" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36786,7 @@
       </c>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36840,7 +36840,7 @@
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36867,7 +36867,7 @@
       </c>
       <c r="E1350" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36894,7 +36894,7 @@
       </c>
       <c r="E1351" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
       </c>
       <c r="E1352" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="E1353" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="E1354" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="E1355" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="E1356" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37056,7 +37056,7 @@
       </c>
       <c r="E1357" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37083,7 +37083,7 @@
       </c>
       <c r="E1358" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37110,7 +37110,7 @@
       </c>
       <c r="E1359" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37137,7 +37137,7 @@
       </c>
       <c r="E1360" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37164,7 +37164,7 @@
       </c>
       <c r="E1361" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="E1362" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37218,7 +37218,7 @@
       </c>
       <c r="E1363" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37299,7 +37299,7 @@
       </c>
       <c r="E1366" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37326,7 +37326,7 @@
       </c>
       <c r="E1367" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37353,7 +37353,7 @@
       </c>
       <c r="E1368" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="E1369" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37407,7 +37407,7 @@
       </c>
       <c r="E1370" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37461,7 +37461,7 @@
       </c>
       <c r="E1372" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="E1373" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37515,7 +37515,7 @@
       </c>
       <c r="E1374" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
       </c>
       <c r="E1375" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37569,7 +37569,7 @@
       </c>
       <c r="E1376" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37596,7 +37596,7 @@
       </c>
       <c r="E1377" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37623,7 +37623,7 @@
       </c>
       <c r="E1378" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37650,7 +37650,7 @@
       </c>
       <c r="E1379" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37677,7 +37677,7 @@
       </c>
       <c r="E1380" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37704,7 +37704,7 @@
       </c>
       <c r="E1381" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="E1382" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37758,7 +37758,7 @@
       </c>
       <c r="E1383" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37785,7 +37785,7 @@
       </c>
       <c r="E1384" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="E1385" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37839,7 +37839,7 @@
       </c>
       <c r="E1386" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -37866,7 +37866,7 @@
       </c>
       <c r="E1387" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.incl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37893,7 +37893,7 @@
       </c>
       <c r="E1388" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 2 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="E1389" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37947,7 +37947,7 @@
       </c>
       <c r="E1390" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E1391" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3 and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38001,7 +38001,7 @@
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: A (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="E1393" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl.excl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 1excl and Role: A (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="E1396" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38136,7 +38136,7 @@
       </c>
       <c r="E1397" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38163,7 +38163,7 @@
       </c>
       <c r="E1398" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38190,7 +38190,7 @@
       </c>
       <c r="E1399" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38217,7 +38217,7 @@
       </c>
       <c r="E1400" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38244,7 @@
       </c>
       <c r="E1401" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38271,7 +38271,7 @@
       </c>
       <c r="E1402" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E1403" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="E1404" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38352,7 +38352,7 @@
       </c>
       <c r="E1405" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38865,7 +38865,7 @@
       </c>
       <c r="E1424" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38892,7 +38892,7 @@
       </c>
       <c r="E1425" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38919,7 +38919,7 @@
       </c>
       <c r="E1426" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38946,7 +38946,7 @@
       </c>
       <c r="E1427" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -38973,7 +38973,7 @@
       </c>
       <c r="E1428" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39000,7 +39000,7 @@
       </c>
       <c r="E1429" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39027,7 +39027,7 @@
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39054,7 +39054,7 @@
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="E1438" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39270,7 +39270,7 @@
       </c>
       <c r="E1439" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39297,7 +39297,7 @@
       </c>
       <c r="E1440" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39324,7 +39324,7 @@
       </c>
       <c r="E1441" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39351,7 +39351,7 @@
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39378,7 +39378,7 @@
       </c>
       <c r="E1443" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39405,7 +39405,7 @@
       </c>
       <c r="E1444" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
       </c>
       <c r="E1445" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39459,7 +39459,7 @@
       </c>
       <c r="E1446" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39540,7 +39540,7 @@
       </c>
       <c r="E1449" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39648,7 +39648,7 @@
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39675,7 +39675,7 @@
       </c>
       <c r="E1454" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39702,7 +39702,7 @@
       </c>
       <c r="E1455" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39729,7 +39729,7 @@
       </c>
       <c r="E1456" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39756,7 +39756,7 @@
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39783,7 +39783,7 @@
       </c>
       <c r="E1458" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39810,7 @@
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39837,7 +39837,7 @@
       </c>
       <c r="E1460" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -39918,7 +39918,7 @@
       </c>
       <c r="E1463" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40053,7 +40053,7 @@
       </c>
       <c r="E1468" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40080,7 +40080,7 @@
       </c>
       <c r="E1469" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40107,7 +40107,7 @@
       </c>
       <c r="E1470" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -40134,7 +40134,7 @@
       </c>
       <c r="E1471" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41673,7 +41673,7 @@
       </c>
       <c r="E1528" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41700,7 +41700,7 @@
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41727,7 +41727,7 @@
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41754,7 +41754,7 @@
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41781,7 +41781,7 @@
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41862,7 +41862,7 @@
       </c>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41889,7 +41889,7 @@
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41916,7 +41916,7 @@
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41943,7 +41943,7 @@
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41970,7 +41970,7 @@
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -41997,7 +41997,7 @@
       </c>
       <c r="E1540" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg-high and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl-low and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42024,7 +42024,7 @@
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42078,7 +42078,7 @@
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42105,7 +42105,7 @@
       </c>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42159,7 +42159,7 @@
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -42949,7 +42949,7 @@
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
@@ -42969,14 +42969,14 @@
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
@@ -42996,14 +42996,14 @@
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>2sg</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
@@ -43023,14 +43023,14 @@
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>language has an inferred gap at reference: 3pl.anim and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>2sg</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
@@ -43050,14 +43050,14 @@
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2sg and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>Verb</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1580" t="inlineStr">
@@ -43077,7 +43077,7 @@
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.inanim and Role: S (INFERRED_NULL_zero)</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role P in language: lako1247, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43158,7 +43158,7 @@
       </c>
       <c r="E1583" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43185,7 +43185,7 @@
       </c>
       <c r="E1584" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43212,7 +43212,7 @@
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.hum and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -43678,7 +43678,7 @@
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1603" t="inlineStr">
@@ -43698,7 +43698,7 @@
       </c>
       <c r="E1603" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43725,14 +43725,14 @@
       </c>
       <c r="E1604" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1605" t="inlineStr">
@@ -43752,7 +43752,7 @@
       </c>
       <c r="E1605" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43786,7 +43786,7 @@
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>2pl</t>
+          <t>1pl.excl</t>
         </is>
       </c>
       <c r="B1607" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="E1607" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -43833,14 +43833,14 @@
       </c>
       <c r="E1608" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>1pl.excl</t>
+          <t>2pl</t>
         </is>
       </c>
       <c r="B1609" t="inlineStr">
@@ -43860,7 +43860,7 @@
       </c>
       <c r="E1609" t="inlineStr">
         <is>
-          <t>WARNING: More possible coarguments than referential types found for reference 1pl.excl and role P in language: swam1239, this is probably due to one or more monoexponential plurals</t>
+          <t>WARNING: More possible coarguments than referential types found for reference 2pl and role A in language: swam1239, this is probably due to one or more monoexponential plurals</t>
         </is>
       </c>
     </row>
@@ -44616,7 +44616,7 @@
       </c>
       <c r="E1637" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44643,7 +44643,7 @@
       </c>
       <c r="E1638" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
       </c>
       <c r="E1639" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: S (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: S (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -44697,7 +44697,7 @@
       </c>
       <c r="E1640" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.hum and Role: A (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.nonhum and Role: A (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -45426,7 +45426,7 @@
       </c>
       <c r="E1667" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="E1669" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45507,7 +45507,7 @@
       </c>
       <c r="E1670" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45534,7 +45534,7 @@
       </c>
       <c r="E1671" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45561,7 +45561,7 @@
       </c>
       <c r="E1672" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45588,7 +45588,7 @@
       </c>
       <c r="E1673" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45615,7 +45615,7 @@
       </c>
       <c r="E1674" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45642,7 +45642,7 @@
       </c>
       <c r="E1675" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="E1676" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="E1677" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45723,7 +45723,7 @@
       </c>
       <c r="E1678" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45750,7 +45750,7 @@
       </c>
       <c r="E1679" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45804,7 +45804,7 @@
       </c>
       <c r="E1681" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45831,7 +45831,7 @@
       </c>
       <c r="E1682" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45858,7 +45858,7 @@
       </c>
       <c r="E1683" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.M and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45885,7 +45885,7 @@
       </c>
       <c r="E1684" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45912,7 +45912,7 @@
       </c>
       <c r="E1685" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2plHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45939,7 +45939,7 @@
       </c>
       <c r="E1686" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45966,7 +45966,7 @@
       </c>
       <c r="E1687" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.M and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -45993,7 +45993,7 @@
       </c>
       <c r="E1688" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46020,7 +46020,7 @@
       </c>
       <c r="E1689" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sgHON and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46047,7 +46047,7 @@
       </c>
       <c r="E1690" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg.F and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl.F and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46236,7 +46236,7 @@
       </c>
       <c r="E1697" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46263,7 +46263,7 @@
       </c>
       <c r="E1698" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46290,7 +46290,7 @@
       </c>
       <c r="E1699" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46317,7 +46317,7 @@
       </c>
       <c r="E1700" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (INFERRED_NULL_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (INFERRED_NULL_zero)</t>
         </is>
       </c>
     </row>
@@ -46533,7 +46533,7 @@
       </c>
       <c r="E1708" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46560,7 +46560,7 @@
       </c>
       <c r="E1709" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46587,7 +46587,7 @@
       </c>
       <c r="E1710" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46641,7 +46641,7 @@
       </c>
       <c r="E1712" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46668,7 +46668,7 @@
       </c>
       <c r="E1713" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46722,7 +46722,7 @@
       </c>
       <c r="E1715" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46749,7 +46749,7 @@
       </c>
       <c r="E1716" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 1sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46776,7 +46776,7 @@
       </c>
       <c r="E1717" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46830,7 +46830,7 @@
       </c>
       <c r="E1719" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 3pl and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
@@ -46857,7 +46857,7 @@
       </c>
       <c r="E1720" t="inlineStr">
         <is>
-          <t>language has an inferred gap at reference: 3sg and Role: P (ROLE_NOT_MARKED_zero)</t>
+          <t>language has an inferred gap at reference: 2sg and Role: P (ROLE_NOT_MARKED_zero)</t>
         </is>
       </c>
     </row>
